--- a/TUCUMAN 1061/Mayo/tucuman MAYO.xlsx
+++ b/TUCUMAN 1061/Mayo/tucuman MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\TUCUMAN 1061\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870BAA73-4CC0-4D56-A490-5DDFA53C92E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3472BD4-0C9F-4F3E-9E64-4DD1A3FCC6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1698,159 +1698,159 @@
     <xf numFmtId="2" fontId="23" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="19" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="36" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="32" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="29" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="32" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="28" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="36" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="35" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="34" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="32" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="29" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="8" borderId="32" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="8" borderId="31" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="8" borderId="30" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2283,10 +2283,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="205">
+      <c r="E3" s="208">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="205"/>
+      <c r="F3" s="208"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -2358,16 +2358,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="215" t="s">
+      <c r="A12" s="218" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="215"/>
-      <c r="C12" s="215"/>
-      <c r="D12" s="215"/>
-      <c r="E12" s="215"/>
-      <c r="F12" s="215"/>
-      <c r="G12" s="215"/>
-      <c r="H12" s="215"/>
+      <c r="B12" s="218"/>
+      <c r="C12" s="218"/>
+      <c r="D12" s="218"/>
+      <c r="E12" s="218"/>
+      <c r="F12" s="218"/>
+      <c r="G12" s="218"/>
+      <c r="H12" s="218"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
@@ -2405,7 +2405,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="251">
+      <c r="H15" s="201">
         <v>4030.28</v>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
-      <c r="H16" s="252">
+      <c r="H16" s="202">
         <f>SUM(H13:H15)</f>
         <v>377620.78</v>
       </c>
@@ -2435,16 +2435,16 @@
       <c r="H17" s="44"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="216" t="s">
+      <c r="A18" s="219" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="217"/>
-      <c r="C18" s="217"/>
-      <c r="D18" s="217"/>
-      <c r="E18" s="217"/>
-      <c r="F18" s="217"/>
-      <c r="G18" s="217"/>
-      <c r="H18" s="218"/>
+      <c r="B18" s="220"/>
+      <c r="C18" s="220"/>
+      <c r="D18" s="220"/>
+      <c r="E18" s="220"/>
+      <c r="F18" s="220"/>
+      <c r="G18" s="220"/>
+      <c r="H18" s="221"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
@@ -2456,8 +2456,8 @@
       <c r="E19" s="19"/>
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="26">
-        <v>183683.96</v>
+      <c r="H19" s="200">
+        <v>186966.9</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -2470,7 +2470,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
-      <c r="H20" s="250">
+      <c r="H20" s="200">
         <v>400523.88</v>
       </c>
     </row>
@@ -2486,27 +2486,27 @@
       <c r="G21" s="22"/>
       <c r="H21" s="27">
         <f>SUM(H19:H20)</f>
-        <v>584207.84</v>
+        <v>587490.78</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="219" t="s">
+      <c r="A22" s="222" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="219"/>
-      <c r="C22" s="219"/>
-      <c r="D22" s="219"/>
-      <c r="E22" s="219"/>
-      <c r="F22" s="219"/>
-      <c r="G22" s="219"/>
-      <c r="H22" s="219"/>
+      <c r="B22" s="222"/>
+      <c r="C22" s="222"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="222"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="201" t="s">
+      <c r="A23" s="204" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="202"/>
-      <c r="C23" s="202"/>
+      <c r="B23" s="205"/>
+      <c r="C23" s="205"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
@@ -2523,7 +2523,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
-      <c r="H24" s="250">
+      <c r="H24" s="200">
         <v>42645</v>
       </c>
       <c r="I24" s="14"/>
@@ -2559,16 +2559,16 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="216" t="s">
+      <c r="A27" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="217"/>
-      <c r="C27" s="217"/>
-      <c r="D27" s="217"/>
-      <c r="E27" s="217"/>
-      <c r="F27" s="217"/>
-      <c r="G27" s="217"/>
-      <c r="H27" s="218"/>
+      <c r="B27" s="220"/>
+      <c r="C27" s="220"/>
+      <c r="D27" s="220"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="220"/>
+      <c r="G27" s="220"/>
+      <c r="H27" s="221"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
@@ -2614,16 +2614,16 @@
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="216" t="s">
+      <c r="A31" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="217"/>
-      <c r="C31" s="217"/>
-      <c r="D31" s="217"/>
-      <c r="E31" s="217"/>
-      <c r="F31" s="217"/>
-      <c r="G31" s="217"/>
-      <c r="H31" s="218"/>
+      <c r="B31" s="220"/>
+      <c r="C31" s="220"/>
+      <c r="D31" s="220"/>
+      <c r="E31" s="220"/>
+      <c r="F31" s="220"/>
+      <c r="G31" s="220"/>
+      <c r="H31" s="221"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="53"/>
@@ -2648,7 +2648,7 @@
       <c r="G33" s="31"/>
       <c r="H33" s="32">
         <f>H16+H21+H26+H29+H32</f>
-        <v>1130066.29</v>
+        <v>1133349.23</v>
       </c>
     </row>
     <row r="34" spans="1:11" s="14" customFormat="1" ht="18" x14ac:dyDescent="0.3">
@@ -2666,69 +2666,69 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="206" t="s">
+      <c r="A35" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="207"/>
-      <c r="C35" s="207"/>
-      <c r="D35" s="207"/>
-      <c r="E35" s="207"/>
-      <c r="F35" s="207"/>
-      <c r="G35" s="207"/>
-      <c r="H35" s="208"/>
+      <c r="B35" s="210"/>
+      <c r="C35" s="210"/>
+      <c r="D35" s="210"/>
+      <c r="E35" s="210"/>
+      <c r="F35" s="210"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="211"/>
       <c r="I35" s="174"/>
       <c r="K35" s="174"/>
     </row>
     <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="209"/>
-      <c r="B36" s="210"/>
-      <c r="C36" s="210"/>
-      <c r="D36" s="210"/>
-      <c r="E36" s="210"/>
-      <c r="F36" s="210"/>
-      <c r="G36" s="210"/>
-      <c r="H36" s="211"/>
+      <c r="A36" s="212"/>
+      <c r="B36" s="213"/>
+      <c r="C36" s="213"/>
+      <c r="D36" s="213"/>
+      <c r="E36" s="213"/>
+      <c r="F36" s="213"/>
+      <c r="G36" s="213"/>
+      <c r="H36" s="214"/>
     </row>
     <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="220"/>
-      <c r="B37" s="221"/>
-      <c r="C37" s="221"/>
-      <c r="D37" s="221"/>
-      <c r="E37" s="221"/>
-      <c r="F37" s="221"/>
-      <c r="G37" s="222"/>
+      <c r="A37" s="223"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="225"/>
       <c r="H37" s="33"/>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="220"/>
-      <c r="B38" s="221"/>
-      <c r="C38" s="221"/>
-      <c r="D38" s="221"/>
-      <c r="E38" s="221"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="222"/>
+      <c r="A38" s="223"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="225"/>
       <c r="H38" s="33"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="223"/>
-      <c r="B39" s="224"/>
-      <c r="C39" s="224"/>
-      <c r="D39" s="224"/>
-      <c r="E39" s="224"/>
-      <c r="F39" s="224"/>
-      <c r="G39" s="225"/>
+      <c r="A39" s="226"/>
+      <c r="B39" s="227"/>
+      <c r="C39" s="227"/>
+      <c r="D39" s="227"/>
+      <c r="E39" s="227"/>
+      <c r="F39" s="227"/>
+      <c r="G39" s="228"/>
       <c r="H39" s="33"/>
     </row>
     <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="226" t="s">
+      <c r="A40" s="229" t="s">
         <v>16</v>
       </c>
-      <c r="B40" s="227"/>
-      <c r="C40" s="227"/>
-      <c r="D40" s="227"/>
-      <c r="E40" s="227"/>
-      <c r="F40" s="227"/>
-      <c r="G40" s="228"/>
+      <c r="B40" s="230"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="231"/>
       <c r="H40" s="34">
         <f>SUM(H37:H39)</f>
         <v>0</v>
@@ -2749,32 +2749,32 @@
       <c r="J42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="200" t="s">
+      <c r="A43" s="203" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="200"/>
-      <c r="C43" s="200"/>
-      <c r="D43" s="200"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
+      <c r="B43" s="203"/>
+      <c r="C43" s="203"/>
+      <c r="D43" s="203"/>
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
       <c r="H43" s="32">
         <f>+H33+H34</f>
-        <v>1305597.47</v>
+        <v>1308880.4099999999</v>
       </c>
       <c r="J43" s="174"/>
     </row>
     <row r="44" spans="1:11" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="203" t="s">
+      <c r="A44" s="206" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="203"/>
-      <c r="C44" s="203"/>
-      <c r="D44" s="203"/>
-      <c r="E44" s="203"/>
-      <c r="F44" s="203"/>
-      <c r="G44" s="203"/>
-      <c r="H44" s="203"/>
+      <c r="B44" s="206"/>
+      <c r="C44" s="206"/>
+      <c r="D44" s="206"/>
+      <c r="E44" s="206"/>
+      <c r="F44" s="206"/>
+      <c r="G44" s="206"/>
+      <c r="H44" s="206"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
@@ -2812,27 +2812,27 @@
       <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:11" ht="18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="212" t="s">
+      <c r="A48" s="215" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="213"/>
-      <c r="C48" s="213"/>
-      <c r="D48" s="213"/>
-      <c r="E48" s="213"/>
-      <c r="F48" s="213"/>
-      <c r="G48" s="213"/>
-      <c r="H48" s="214"/>
+      <c r="B48" s="216"/>
+      <c r="C48" s="216"/>
+      <c r="D48" s="216"/>
+      <c r="E48" s="216"/>
+      <c r="F48" s="216"/>
+      <c r="G48" s="216"/>
+      <c r="H48" s="217"/>
     </row>
     <row r="49" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="204" t="s">
+      <c r="A49" s="207" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="204"/>
-      <c r="C49" s="204"/>
-      <c r="D49" s="204"/>
-      <c r="E49" s="204"/>
-      <c r="F49" s="204"/>
-      <c r="G49" s="204"/>
+      <c r="B49" s="207"/>
+      <c r="C49" s="207"/>
+      <c r="D49" s="207"/>
+      <c r="E49" s="207"/>
+      <c r="F49" s="207"/>
+      <c r="G49" s="207"/>
       <c r="H49" s="41">
         <v>-33418.360562974354</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="G52" s="37"/>
       <c r="H52" s="38">
         <f>-(H33+H40)</f>
-        <v>-1130066.29</v>
+        <v>-1133349.23</v>
       </c>
       <c r="J52" s="15"/>
     </row>
@@ -2894,7 +2894,7 @@
       <c r="G53" s="40"/>
       <c r="H53" s="52">
         <f>SUM(H49:H52)</f>
-        <v>798478.00844455743</v>
+        <v>795195.06844455749</v>
       </c>
     </row>
   </sheetData>
@@ -2955,27 +2955,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="232" t="str">
+      <c r="A1" s="235" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: MAYO </v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="234"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
+      <c r="Q1" s="236"/>
+      <c r="R1" s="237"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="97"/>
@@ -3003,12 +3003,12 @@
       <c r="I4" s="59"/>
       <c r="J4" s="59"/>
       <c r="L4" s="95"/>
-      <c r="M4" s="230"/>
-      <c r="N4" s="230"/>
-      <c r="O4" s="230"/>
-      <c r="P4" s="230"/>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="231"/>
+      <c r="M4" s="233"/>
+      <c r="N4" s="233"/>
+      <c r="O4" s="233"/>
+      <c r="P4" s="233"/>
+      <c r="Q4" s="233"/>
+      <c r="R4" s="234"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="93"/>
@@ -3044,11 +3044,11 @@
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="93"/>
       <c r="B7" s="92"/>
-      <c r="C7" s="240">
+      <c r="C7" s="243">
         <f>C5</f>
         <v>1299999.9999999998</v>
       </c>
-      <c r="D7" s="240"/>
+      <c r="D7" s="243"/>
       <c r="E7" s="94"/>
       <c r="G7" s="59"/>
       <c r="H7" s="59"/>
@@ -4334,9 +4334,9 @@
       </c>
     </row>
     <row r="32" spans="1:21" s="61" customFormat="1" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="238"/>
-      <c r="B32" s="239"/>
-      <c r="C32" s="239"/>
+      <c r="A32" s="241"/>
+      <c r="B32" s="242"/>
+      <c r="C32" s="242"/>
       <c r="D32" s="68"/>
       <c r="E32" s="68"/>
       <c r="F32" s="102"/>
@@ -4378,25 +4378,25 @@
       </c>
     </row>
     <row r="33" spans="2:21" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="235" t="s">
+      <c r="B33" s="238" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="236"/>
-      <c r="D33" s="236"/>
-      <c r="E33" s="236"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="236"/>
-      <c r="H33" s="236"/>
-      <c r="I33" s="236"/>
-      <c r="J33" s="236"/>
-      <c r="K33" s="236"/>
-      <c r="L33" s="236"/>
-      <c r="M33" s="236"/>
-      <c r="N33" s="236"/>
-      <c r="O33" s="236"/>
-      <c r="P33" s="236"/>
-      <c r="Q33" s="236"/>
-      <c r="R33" s="237"/>
+      <c r="C33" s="239"/>
+      <c r="D33" s="239"/>
+      <c r="E33" s="239"/>
+      <c r="F33" s="239"/>
+      <c r="G33" s="239"/>
+      <c r="H33" s="239"/>
+      <c r="I33" s="239"/>
+      <c r="J33" s="239"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
+      <c r="M33" s="239"/>
+      <c r="N33" s="239"/>
+      <c r="O33" s="239"/>
+      <c r="P33" s="239"/>
+      <c r="Q33" s="239"/>
+      <c r="R33" s="240"/>
       <c r="U33" s="99" t="s">
         <v>58</v>
       </c>
@@ -4416,81 +4416,81 @@
       </c>
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C35" s="229" t="s">
+      <c r="C35" s="232" t="s">
         <v>159</v>
       </c>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="229"/>
-      <c r="O35" s="229"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="232"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="232"/>
+      <c r="O35" s="232"/>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="229"/>
+      <c r="C36" s="232"/>
+      <c r="D36" s="232"/>
+      <c r="E36" s="232"/>
+      <c r="F36" s="232"/>
+      <c r="G36" s="232"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="232"/>
+      <c r="O36" s="232"/>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="229"/>
-      <c r="J37" s="229"/>
-      <c r="K37" s="229"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="229"/>
-      <c r="N37" s="229"/>
-      <c r="O37" s="229"/>
+      <c r="C37" s="232"/>
+      <c r="D37" s="232"/>
+      <c r="E37" s="232"/>
+      <c r="F37" s="232"/>
+      <c r="G37" s="232"/>
+      <c r="H37" s="232"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="232"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="232"/>
+      <c r="O37" s="232"/>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="C38" s="229"/>
-      <c r="D38" s="229"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
-      <c r="G38" s="229"/>
-      <c r="H38" s="229"/>
-      <c r="I38" s="229"/>
-      <c r="J38" s="229"/>
-      <c r="K38" s="229"/>
-      <c r="L38" s="229"/>
-      <c r="M38" s="229"/>
-      <c r="N38" s="229"/>
-      <c r="O38" s="229"/>
+      <c r="C38" s="232"/>
+      <c r="D38" s="232"/>
+      <c r="E38" s="232"/>
+      <c r="F38" s="232"/>
+      <c r="G38" s="232"/>
+      <c r="H38" s="232"/>
+      <c r="I38" s="232"/>
+      <c r="J38" s="232"/>
+      <c r="K38" s="232"/>
+      <c r="L38" s="232"/>
+      <c r="M38" s="232"/>
+      <c r="N38" s="232"/>
+      <c r="O38" s="232"/>
     </row>
     <row r="39" spans="2:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="229"/>
-      <c r="D39" s="229"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
-      <c r="G39" s="229"/>
-      <c r="H39" s="229"/>
-      <c r="I39" s="229"/>
-      <c r="J39" s="229"/>
-      <c r="K39" s="229"/>
-      <c r="L39" s="229"/>
-      <c r="M39" s="229"/>
-      <c r="N39" s="229"/>
-      <c r="O39" s="229"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
+      <c r="I39" s="232"/>
+      <c r="J39" s="232"/>
+      <c r="K39" s="232"/>
+      <c r="L39" s="232"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="232"/>
+      <c r="O39" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4526,13 +4526,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="244" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="243"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="246"/>
     </row>
     <row r="2" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="161"/>
@@ -4587,16 +4587,16 @@
       <c r="E6" s="153"/>
     </row>
     <row r="7" spans="1:15" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="244" t="s">
+      <c r="A7" s="247" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="245"/>
-      <c r="C7" s="245"/>
-      <c r="D7" s="245"/>
-      <c r="E7" s="245"/>
-      <c r="F7" s="245"/>
-      <c r="G7" s="245"/>
-      <c r="H7" s="246"/>
+      <c r="B7" s="248"/>
+      <c r="C7" s="248"/>
+      <c r="D7" s="248"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="248"/>
+      <c r="H7" s="249"/>
       <c r="L7" s="120" t="s">
         <v>76</v>
       </c>
@@ -5180,13 +5180,13 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="250" t="s">
         <v>143</v>
       </c>
-      <c r="C28" s="248"/>
-      <c r="D28" s="248"/>
-      <c r="E28" s="248"/>
-      <c r="F28" s="249"/>
+      <c r="C28" s="251"/>
+      <c r="D28" s="251"/>
+      <c r="E28" s="251"/>
+      <c r="F28" s="252"/>
       <c r="J28" s="120">
         <v>176</v>
       </c>

--- a/TUCUMAN 1061/Mayo/tucuman MAYO.xlsx
+++ b/TUCUMAN 1061/Mayo/tucuman MAYO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\TUCUMAN 1061\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00EB6C1-E48B-4E16-96B7-80FB45C7D2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752A60C2-C856-41E2-9B40-D9C0C94BD4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gastos" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Calculo Servicios  (2)'!$A$6:$H$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Gastos!$A$1:$H$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$R$39</definedName>
     <definedName name="CantOper" localSheetId="2">#REF!</definedName>
     <definedName name="CantOper">#REF!</definedName>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="167">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>EDESUR:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglo Lema ascensores - Reposicion y colocacion patin ascensor </t>
   </si>
 </sst>
 </file>
@@ -1665,6 +1668,13 @@
     <xf numFmtId="167" fontId="18" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1806,13 +1816,6 @@
     <xf numFmtId="1" fontId="27" fillId="8" borderId="29" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2211,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -2245,10 +2248,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="198">
+      <c r="E3" s="201">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="198"/>
+      <c r="F3" s="201"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2320,16 +2323,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="208" t="s">
+      <c r="A12" s="211" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="208"/>
-      <c r="C12" s="208"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="208"/>
-      <c r="G12" s="208"/>
-      <c r="H12" s="208"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="211"/>
+      <c r="H12" s="211"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
@@ -2397,16 +2400,16 @@
       <c r="H17" s="43"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="209" t="s">
+      <c r="A18" s="212" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="210"/>
-      <c r="C18" s="210"/>
-      <c r="D18" s="210"/>
-      <c r="E18" s="210"/>
-      <c r="F18" s="210"/>
-      <c r="G18" s="210"/>
-      <c r="H18" s="211"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="213"/>
+      <c r="D18" s="213"/>
+      <c r="E18" s="213"/>
+      <c r="F18" s="213"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="214"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
@@ -2452,23 +2455,23 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="212" t="s">
+      <c r="A22" s="215" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="212"/>
-      <c r="C22" s="212"/>
-      <c r="D22" s="212"/>
-      <c r="E22" s="212"/>
-      <c r="F22" s="212"/>
-      <c r="G22" s="212"/>
-      <c r="H22" s="212"/>
+      <c r="B22" s="215"/>
+      <c r="C22" s="215"/>
+      <c r="D22" s="215"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="215"/>
+      <c r="G22" s="215"/>
+      <c r="H22" s="215"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="100" t="s">
         <v>162</v>
       </c>
-      <c r="B23" s="243"/>
-      <c r="C23" s="243"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="196"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
@@ -2495,154 +2498,158 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="100" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="26">
+        <v>380000</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="26">
         <v>65000</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="27">
-        <f>SUM(H23:H25)</f>
-        <v>704443.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="209" t="s">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="27">
+        <f>SUM(H23:H26)</f>
+        <v>1084443.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="212" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="210"/>
-      <c r="C27" s="210"/>
-      <c r="D27" s="210"/>
-      <c r="E27" s="210"/>
-      <c r="F27" s="210"/>
-      <c r="G27" s="210"/>
-      <c r="H27" s="211"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="B28" s="213"/>
+      <c r="C28" s="213"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="213"/>
+      <c r="F28" s="213"/>
+      <c r="G28" s="213"/>
+      <c r="H28" s="214"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19" t="s">
+      <c r="B29" s="19"/>
+      <c r="C29" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="46"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="46"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="187">
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="187">
         <v>60592.67</v>
       </c>
-      <c r="I29" s="46"/>
-      <c r="N29" t="s">
+      <c r="I30" s="46"/>
+      <c r="N30" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="29"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="209" t="s">
+    <row r="31" spans="1:14" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="29"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="212" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="210"/>
-      <c r="C31" s="210"/>
-      <c r="D31" s="210"/>
-      <c r="E31" s="210"/>
-      <c r="F31" s="210"/>
-      <c r="G31" s="210"/>
-      <c r="H31" s="211"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="54"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="B32" s="213"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="213"/>
+      <c r="E32" s="213"/>
+      <c r="F32" s="213"/>
+      <c r="G32" s="213"/>
+      <c r="H32" s="214"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32">
-        <f>H16+H21+H26+H29+H32</f>
-        <v>1730147.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="48" t="s">
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32">
+        <f>H16+H21+H27+H30+H33</f>
+        <v>2110147.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="50"/>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="199" t="s">
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="50"/>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="202" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="200"/>
-      <c r="C35" s="200"/>
-      <c r="D35" s="200"/>
-      <c r="E35" s="200"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="170"/>
-      <c r="K35" s="170"/>
-    </row>
-    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="202"/>
       <c r="B36" s="203"/>
       <c r="C36" s="203"/>
       <c r="D36" s="203"/>
@@ -2650,28 +2657,30 @@
       <c r="F36" s="203"/>
       <c r="G36" s="203"/>
       <c r="H36" s="204"/>
-    </row>
-    <row r="37" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="213"/>
-      <c r="B37" s="214"/>
-      <c r="C37" s="214"/>
-      <c r="D37" s="214"/>
-      <c r="E37" s="214"/>
-      <c r="F37" s="214"/>
-      <c r="G37" s="215"/>
-      <c r="H37" s="33"/>
+      <c r="I36" s="170"/>
+      <c r="K36" s="170"/>
+    </row>
+    <row r="37" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="205"/>
+      <c r="B37" s="206"/>
+      <c r="C37" s="206"/>
+      <c r="D37" s="206"/>
+      <c r="E37" s="206"/>
+      <c r="F37" s="206"/>
+      <c r="G37" s="206"/>
+      <c r="H37" s="207"/>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="213"/>
-      <c r="B38" s="214"/>
-      <c r="C38" s="214"/>
-      <c r="D38" s="214"/>
-      <c r="E38" s="214"/>
-      <c r="F38" s="214"/>
-      <c r="G38" s="215"/>
+      <c r="A38" s="216"/>
+      <c r="B38" s="217"/>
+      <c r="C38" s="217"/>
+      <c r="D38" s="217"/>
+      <c r="E38" s="217"/>
+      <c r="F38" s="217"/>
+      <c r="G38" s="218"/>
       <c r="H38" s="33"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="216"/>
       <c r="B39" s="217"/>
       <c r="C39" s="217"/>
@@ -2681,130 +2690,125 @@
       <c r="G39" s="218"/>
       <c r="H39" s="33"/>
     </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="219" t="s">
-        <v>16</v>
-      </c>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="219"/>
       <c r="B40" s="220"/>
       <c r="C40" s="220"/>
       <c r="D40" s="220"/>
       <c r="E40" s="220"/>
       <c r="F40" s="220"/>
       <c r="G40" s="221"/>
-      <c r="H40" s="34">
-        <f>SUM(H37:H39)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="33"/>
+    </row>
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="222" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="223"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="223"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="224"/>
+      <c r="H41" s="34">
+        <f>SUM(H38:H40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="19"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
       <c r="H42" s="19"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="196" t="s">
+    </row>
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="19"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="199" t="s">
         <v>146</v>
       </c>
-      <c r="B43" s="196"/>
-      <c r="C43" s="196"/>
-      <c r="D43" s="196"/>
-      <c r="E43" s="196"/>
-      <c r="F43" s="196"/>
-      <c r="G43" s="196"/>
-      <c r="H43" s="32">
-        <f>+H33+H34</f>
-        <v>1730147.75</v>
-      </c>
-      <c r="J43" s="170"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="19"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
+      <c r="B44" s="199"/>
+      <c r="C44" s="199"/>
+      <c r="D44" s="199"/>
+      <c r="E44" s="199"/>
+      <c r="F44" s="199"/>
+      <c r="G44" s="199"/>
+      <c r="H44" s="32">
+        <f>+H34+H35</f>
+        <v>2110147.75</v>
+      </c>
+      <c r="J44" s="170"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="35">
-        <f>H40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="19"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="205" t="s">
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="35">
+        <f>H41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="206"/>
-      <c r="C47" s="206"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
-      <c r="F47" s="206"/>
-      <c r="G47" s="206"/>
-      <c r="H47" s="207"/>
-    </row>
-    <row r="48" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="197" t="s">
+      <c r="B48" s="209"/>
+      <c r="C48" s="209"/>
+      <c r="D48" s="209"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="210"/>
+    </row>
+    <row r="49" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="200" t="s">
         <v>153</v>
       </c>
-      <c r="B48" s="197"/>
-      <c r="C48" s="197"/>
-      <c r="D48" s="197"/>
-      <c r="E48" s="197"/>
-      <c r="F48" s="197"/>
-      <c r="G48" s="197"/>
-      <c r="H48" s="41">
+      <c r="B49" s="200"/>
+      <c r="C49" s="200"/>
+      <c r="D49" s="200"/>
+      <c r="E49" s="200"/>
+      <c r="F49" s="200"/>
+      <c r="G49" s="200"/>
+      <c r="H49" s="41">
         <v>804075.47844455764</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="47">
-        <f>Planilla!I31</f>
-        <v>2414480.2154854122</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50" s="37"/>
       <c r="C50" s="37"/>
@@ -2812,43 +2816,58 @@
       <c r="E50" s="37"/>
       <c r="F50" s="37"/>
       <c r="G50" s="37"/>
-      <c r="H50" s="38">
-        <f>-(H33+H40)</f>
-        <v>-1730147.75</v>
-      </c>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A51" s="39" t="s">
+      <c r="H50" s="47">
+        <f>Planilla!I31</f>
+        <v>2414480.2154854122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="38">
+        <f>-(H34+H41)</f>
+        <v>-2110147.75</v>
+      </c>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A52" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="51">
-        <f>SUM(H48:H50)</f>
-        <v>1488407.9439299698</v>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="51">
+        <f>SUM(H49:H51)</f>
+        <v>1108407.9439299698</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A35:H36"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2889,32 +2908,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="225" t="str">
+      <c r="A1" s="228" t="str">
         <f>Gastos!E7</f>
         <v xml:space="preserve">PERIODO: MAYO </v>
       </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="227"/>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="230"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="94"/>
-      <c r="C2" s="245">
-        <v>1299999.9999999998</v>
+      <c r="C2" s="198">
+        <v>1500000</v>
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="58"/>
@@ -2926,7 +2945,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="90"/>
-      <c r="D3" s="245">
+      <c r="D3" s="198">
         <v>400523.88</v>
       </c>
       <c r="G3" s="58"/>
@@ -2947,21 +2966,21 @@
       <c r="I4" s="58"/>
       <c r="J4" s="58"/>
       <c r="L4" s="92"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
-      <c r="R4" s="224"/>
+      <c r="M4" s="226"/>
+      <c r="N4" s="226"/>
+      <c r="O4" s="226"/>
+      <c r="P4" s="226"/>
+      <c r="Q4" s="226"/>
+      <c r="R4" s="227"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="90"/>
       <c r="B5" s="93"/>
-      <c r="C5" s="233">
+      <c r="C5" s="236">
         <f>D3</f>
         <v>400523.88</v>
       </c>
-      <c r="D5" s="233"/>
+      <c r="D5" s="236"/>
       <c r="E5" s="13"/>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -2989,11 +3008,11 @@
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="90"/>
       <c r="B7" s="89"/>
-      <c r="C7" s="233">
+      <c r="C7" s="236">
         <f>C2-D3</f>
-        <v>899476.11999999976</v>
-      </c>
-      <c r="D7" s="233"/>
+        <v>1099476.1200000001</v>
+      </c>
+      <c r="D7" s="236"/>
       <c r="E7" s="91"/>
       <c r="G7" s="58"/>
       <c r="H7" s="58"/>
@@ -3138,11 +3157,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="69">
-        <f t="shared" ref="O11:Q29" si="2">C$7*F11/100</f>
-        <v>71058.613479999985</v>
+        <f>C$7*F11/100</f>
+        <v>86858.613480000015</v>
       </c>
       <c r="P11" s="69">
-        <f t="shared" ref="P11:P30" si="3">C$9*F11/100</f>
+        <f t="shared" ref="P11:P30" si="2">C$9*F11/100</f>
         <v>0</v>
       </c>
       <c r="Q11" s="69">
@@ -3150,8 +3169,8 @@
         <v>31641.386520000004</v>
       </c>
       <c r="R11" s="193">
-        <f>O11+N11+P11+Q11</f>
-        <v>102699.99999999999</v>
+        <f t="shared" ref="R11:R29" si="3">O11+N11+P11+Q11</f>
+        <v>118500.00000000001</v>
       </c>
       <c r="U11" s="95" t="s">
         <v>34</v>
@@ -3200,20 +3219,20 @@
         <v>0</v>
       </c>
       <c r="O12" s="162">
+        <f t="shared" ref="O11:O29" si="5">C$7*F12/100</f>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P12" s="162">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P12" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="69">
+        <f t="shared" ref="Q12:Q22" si="6">C$5*F12/100</f>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R12" s="168">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="69">
-        <f t="shared" ref="Q12:Q22" si="5">C$5*F12/100</f>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R12" s="168">
-        <f>O12+N12+P12+Q12</f>
-        <v>102699.99999999999</v>
+        <v>118500.00000000001</v>
       </c>
       <c r="U12" s="96" t="s">
         <v>35</v>
@@ -3261,20 +3280,20 @@
         <v>528153.19954050239</v>
       </c>
       <c r="O13" s="183">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P13" s="183">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P13" s="183">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="182">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R13" s="184">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="182">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R13" s="184">
-        <f>O13+N13+P13+Q13</f>
-        <v>630853.19954050239</v>
+        <v>646653.19954050251</v>
       </c>
       <c r="U13" s="96" t="s">
         <v>36</v>
@@ -3321,20 +3340,20 @@
         <v>-2.06</v>
       </c>
       <c r="O14" s="67">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P14" s="67">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P14" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R14" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R14" s="66">
-        <f>O14+N14+P14+Q14</f>
-        <v>102697.93999999999</v>
+        <v>118497.94000000002</v>
       </c>
       <c r="U14" s="96" t="s">
         <v>37</v>
@@ -3383,20 +3402,20 @@
         <v>111210.60368119659</v>
       </c>
       <c r="O15" s="67">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P15" s="67">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P15" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R15" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R15" s="66">
-        <f>O15+N15+P15+Q15</f>
-        <v>213910.60368119658</v>
+        <v>229710.6036811966</v>
       </c>
       <c r="U15" s="96" t="s">
         <v>38</v>
@@ -3442,20 +3461,20 @@
         <v>706394.30490492622</v>
       </c>
       <c r="O16" s="183">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P16" s="183">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P16" s="183">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="182">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R16" s="184">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="182">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R16" s="184">
-        <f>O16+N16+P16+Q16</f>
-        <v>809094.30490492622</v>
+        <v>824894.30490492634</v>
       </c>
       <c r="U16" s="96" t="s">
         <v>39</v>
@@ -3506,20 +3525,20 @@
         <v>27057.979022115611</v>
       </c>
       <c r="O17" s="67">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P17" s="67">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P17" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R17" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R17" s="66">
-        <f>O17+N17+P17+Q17</f>
-        <v>129757.9790221156</v>
+        <v>145557.97902211564</v>
       </c>
       <c r="U17" s="96" t="s">
         <v>40</v>
@@ -3570,20 +3589,20 @@
         <v>195038.37315287694</v>
       </c>
       <c r="O18" s="162">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P18" s="162">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P18" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R18" s="168">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R18" s="168">
-        <f>O18+N18+P18+Q18</f>
-        <v>297738.37315287691</v>
+        <v>313538.37315287697</v>
       </c>
       <c r="U18" s="96" t="s">
         <v>41</v>
@@ -3618,7 +3637,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="K19" s="162">
-        <f t="shared" ref="K19:K29" si="6">G19-H19-I19</f>
+        <f t="shared" ref="K19:K29" si="7">G19-H19-I19</f>
         <v>-456.94193710293621</v>
       </c>
       <c r="L19" s="162">
@@ -3634,20 +3653,20 @@
         <v>-941.30039043204852</v>
       </c>
       <c r="O19" s="162">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P19" s="162">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P19" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R19" s="168">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R19" s="168">
-        <f>O19+N19+P19+Q19</f>
-        <v>101758.69960956794</v>
+        <v>117558.69960956796</v>
       </c>
       <c r="U19" s="96" t="s">
         <v>42</v>
@@ -3678,7 +3697,7 @@
       </c>
       <c r="J20" s="67"/>
       <c r="K20" s="67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>27674.957447903405</v>
       </c>
       <c r="L20" s="67"/>
@@ -3687,24 +3706,24 @@
         <v>830.24872343710217</v>
       </c>
       <c r="N20" s="66">
-        <f t="shared" ref="N20:N29" si="7">K20+M20+L20</f>
+        <f t="shared" ref="N20:N29" si="8">K20+M20+L20</f>
         <v>28505.206171340509</v>
       </c>
       <c r="O20" s="67">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P20" s="67">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P20" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R20" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R20" s="66">
-        <f>O20+N20+P20+Q20</f>
-        <v>131205.20617134051</v>
+        <v>147005.20617134054</v>
       </c>
       <c r="U20" s="96" t="s">
         <v>43</v>
@@ -3737,7 +3756,7 @@
       </c>
       <c r="J21" s="162"/>
       <c r="K21" s="162">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17460851965006441</v>
       </c>
       <c r="L21" s="162"/>
@@ -3746,24 +3765,24 @@
         <v>5.2382555895019323E-3</v>
       </c>
       <c r="N21" s="168">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17984677523956635</v>
       </c>
       <c r="O21" s="162">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P21" s="162">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P21" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R21" s="168">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R21" s="168">
-        <f>O21+N21+P21+Q21</f>
-        <v>102700.17984677522</v>
+        <v>118500.17984677525</v>
       </c>
       <c r="U21" s="96" t="s">
         <v>44</v>
@@ -3796,7 +3815,7 @@
       </c>
       <c r="J22" s="162"/>
       <c r="K22" s="162">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L22" s="162"/>
@@ -3805,24 +3824,24 @@
         <v>0</v>
       </c>
       <c r="N22" s="168">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O22" s="162">
+        <f t="shared" si="5"/>
+        <v>86858.613480000015</v>
+      </c>
+      <c r="P22" s="162">
         <f t="shared" si="2"/>
-        <v>71058.613479999985</v>
-      </c>
-      <c r="P22" s="162">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="69">
+        <f t="shared" si="6"/>
+        <v>31641.386520000004</v>
+      </c>
+      <c r="R22" s="168">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="69">
-        <f t="shared" si="5"/>
-        <v>31641.386520000004</v>
-      </c>
-      <c r="R22" s="168">
-        <f>O22+N22+P22+Q22</f>
-        <v>102699.99999999999</v>
+        <v>118500.00000000001</v>
       </c>
       <c r="S22" s="194"/>
       <c r="U22" s="96" t="s">
@@ -3855,7 +3874,7 @@
       </c>
       <c r="J23" s="67"/>
       <c r="K23" s="67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L23" s="67"/>
@@ -3864,21 +3883,21 @@
         <v>0</v>
       </c>
       <c r="N23" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O23" s="67">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P23" s="67">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P23" s="67">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q23" s="67"/>
       <c r="R23" s="66">
-        <f>O23+N23+P23+Q23</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U23" s="96" t="s">
         <v>46</v>
@@ -3910,7 +3929,7 @@
       </c>
       <c r="J24" s="162"/>
       <c r="K24" s="162">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L24" s="162"/>
@@ -3919,15 +3938,15 @@
         <v>0</v>
       </c>
       <c r="N24" s="168">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O24" s="162">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P24" s="162">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P24" s="162">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q24" s="162">
@@ -3935,8 +3954,8 @@
         <v>0</v>
       </c>
       <c r="R24" s="168">
-        <f>O24+N24+P24+Q24</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U24" s="96" t="s">
         <v>47</v>
@@ -3961,12 +3980,12 @@
       </c>
       <c r="H25" s="67"/>
       <c r="I25" s="69">
-        <f t="shared" ref="I25" si="8">G25</f>
+        <f t="shared" ref="I25" si="9">G25</f>
         <v>9619.9999999999982</v>
       </c>
       <c r="J25" s="67"/>
       <c r="K25" s="67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L25" s="67"/>
@@ -3975,15 +3994,15 @@
         <v>0</v>
       </c>
       <c r="N25" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O25" s="67">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P25" s="67">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P25" s="67">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q25" s="67">
@@ -3991,8 +4010,8 @@
         <v>0</v>
       </c>
       <c r="R25" s="66">
-        <f>O25+N25+P25+Q25</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U25" s="96" t="s">
         <v>48</v>
@@ -4029,7 +4048,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="K26" s="162">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L26" s="162"/>
@@ -4038,15 +4057,15 @@
         <v>0</v>
       </c>
       <c r="N26" s="168">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O26" s="162">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P26" s="162">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P26" s="162">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q26" s="162">
@@ -4054,8 +4073,8 @@
         <v>0</v>
       </c>
       <c r="R26" s="168">
-        <f>O26+N26+P26+Q26</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U26" s="96" t="s">
         <v>49</v>
@@ -4090,7 +4109,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="K27" s="67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L27" s="67"/>
@@ -4099,15 +4118,15 @@
         <v>0</v>
       </c>
       <c r="N27" s="66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O27" s="67">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P27" s="67">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P27" s="67">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q27" s="67">
@@ -4115,8 +4134,8 @@
         <v>0</v>
       </c>
       <c r="R27" s="66">
-        <f>O27+N27+P27+Q27</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U27" s="96" t="s">
         <v>50</v>
@@ -4147,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="183">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>54169.696656614957</v>
       </c>
       <c r="L28" s="183"/>
@@ -4156,15 +4175,15 @@
         <v>1625.0908996984485</v>
       </c>
       <c r="N28" s="184">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>55794.787556313408</v>
       </c>
       <c r="O28" s="183">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P28" s="183">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P28" s="183">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q28" s="183">
@@ -4172,8 +4191,8 @@
         <v>0</v>
       </c>
       <c r="R28" s="184">
-        <f>O28+N28+P28+Q28</f>
-        <v>62450.910844313403</v>
+        <f t="shared" si="3"/>
+        <v>63930.91084431341</v>
       </c>
       <c r="U28" s="96" t="s">
         <v>51</v>
@@ -4192,7 +4211,7 @@
       <c r="E29" s="166" t="s">
         <v>156</v>
       </c>
-      <c r="F29" s="244">
+      <c r="F29" s="197">
         <v>0.74</v>
       </c>
       <c r="G29" s="69">
@@ -4210,7 +4229,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="K29" s="162">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L29" s="162"/>
@@ -4219,15 +4238,15 @@
         <v>0</v>
       </c>
       <c r="N29" s="168">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O29" s="162">
+        <f t="shared" si="5"/>
+        <v>8136.1232879999998</v>
+      </c>
+      <c r="P29" s="162">
         <f t="shared" si="2"/>
-        <v>6656.123287999998</v>
-      </c>
-      <c r="P29" s="162">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q29" s="162">
@@ -4235,8 +4254,8 @@
         <v>0</v>
       </c>
       <c r="R29" s="168">
-        <f>O29+N29+P29+Q29</f>
-        <v>6656.123287999998</v>
+        <f t="shared" si="3"/>
+        <v>8136.1232879999998</v>
       </c>
       <c r="U29" s="97" t="s">
         <v>52</v>
@@ -4261,7 +4280,7 @@
       <c r="N30" s="66"/>
       <c r="O30" s="67"/>
       <c r="P30" s="67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q30" s="67"/>
@@ -4271,9 +4290,9 @@
       </c>
     </row>
     <row r="31" spans="1:21" s="60" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="231"/>
-      <c r="B31" s="232"/>
-      <c r="C31" s="232"/>
+      <c r="A31" s="234"/>
+      <c r="B31" s="235"/>
+      <c r="C31" s="235"/>
       <c r="D31" s="65"/>
       <c r="E31" s="65"/>
       <c r="F31" s="99"/>
@@ -4299,44 +4318,44 @@
       <c r="N31" s="61"/>
       <c r="O31" s="64">
         <f>SUM(O11:O30)</f>
-        <v>899296.22477599967</v>
+        <v>1099256.2247760003</v>
       </c>
       <c r="P31" s="64">
-        <f t="shared" ref="P31:Q31" si="9">SUM(P11:P30)</f>
+        <f t="shared" ref="P31:Q31" si="10">SUM(P11:P30)</f>
         <v>0</v>
       </c>
       <c r="Q31" s="64">
-        <f t="shared" si="9"/>
+        <f>SUM(Q11:Q30)</f>
         <v>379696.63824000006</v>
       </c>
       <c r="R31" s="112">
         <f>O31+N31+P31+Q31</f>
-        <v>1278992.8630159998</v>
+        <v>1478952.8630160003</v>
       </c>
       <c r="U31" s="96" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="228" t="s">
+      <c r="B32" s="231" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="229"/>
-      <c r="I32" s="229"/>
-      <c r="J32" s="229"/>
-      <c r="K32" s="229"/>
-      <c r="L32" s="229"/>
-      <c r="M32" s="229"/>
-      <c r="N32" s="229"/>
-      <c r="O32" s="229"/>
-      <c r="P32" s="229"/>
-      <c r="Q32" s="229"/>
-      <c r="R32" s="230"/>
+      <c r="C32" s="232"/>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="232"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="232"/>
+      <c r="J32" s="232"/>
+      <c r="K32" s="232"/>
+      <c r="L32" s="232"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="232"/>
+      <c r="P32" s="232"/>
+      <c r="Q32" s="232"/>
+      <c r="R32" s="233"/>
       <c r="U32" s="96" t="s">
         <v>55</v>
       </c>
@@ -4356,81 +4375,81 @@
       </c>
     </row>
     <row r="34" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C34" s="222" t="s">
+      <c r="C34" s="225" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
-      <c r="G34" s="222"/>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
-      <c r="L34" s="222"/>
-      <c r="M34" s="222"/>
-      <c r="N34" s="222"/>
-      <c r="O34" s="222"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="225"/>
+      <c r="K34" s="225"/>
+      <c r="L34" s="225"/>
+      <c r="M34" s="225"/>
+      <c r="N34" s="225"/>
+      <c r="O34" s="225"/>
     </row>
     <row r="35" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C35" s="222"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
-      <c r="L35" s="222"/>
-      <c r="M35" s="222"/>
-      <c r="N35" s="222"/>
-      <c r="O35" s="222"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="225"/>
+      <c r="N35" s="225"/>
+      <c r="O35" s="225"/>
     </row>
     <row r="36" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C36" s="222"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
-      <c r="G36" s="222"/>
-      <c r="H36" s="222"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="222"/>
-      <c r="K36" s="222"/>
-      <c r="L36" s="222"/>
-      <c r="M36" s="222"/>
-      <c r="N36" s="222"/>
-      <c r="O36" s="222"/>
+      <c r="C36" s="225"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
+      <c r="G36" s="225"/>
+      <c r="H36" s="225"/>
+      <c r="I36" s="225"/>
+      <c r="J36" s="225"/>
+      <c r="K36" s="225"/>
+      <c r="L36" s="225"/>
+      <c r="M36" s="225"/>
+      <c r="N36" s="225"/>
+      <c r="O36" s="225"/>
     </row>
     <row r="37" spans="3:21" x14ac:dyDescent="0.25">
-      <c r="C37" s="222"/>
-      <c r="D37" s="222"/>
-      <c r="E37" s="222"/>
-      <c r="F37" s="222"/>
-      <c r="G37" s="222"/>
-      <c r="H37" s="222"/>
-      <c r="I37" s="222"/>
-      <c r="J37" s="222"/>
-      <c r="K37" s="222"/>
-      <c r="L37" s="222"/>
-      <c r="M37" s="222"/>
-      <c r="N37" s="222"/>
-      <c r="O37" s="222"/>
+      <c r="C37" s="225"/>
+      <c r="D37" s="225"/>
+      <c r="E37" s="225"/>
+      <c r="F37" s="225"/>
+      <c r="G37" s="225"/>
+      <c r="H37" s="225"/>
+      <c r="I37" s="225"/>
+      <c r="J37" s="225"/>
+      <c r="K37" s="225"/>
+      <c r="L37" s="225"/>
+      <c r="M37" s="225"/>
+      <c r="N37" s="225"/>
+      <c r="O37" s="225"/>
     </row>
     <row r="38" spans="3:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="222"/>
-      <c r="D38" s="222"/>
-      <c r="E38" s="222"/>
-      <c r="F38" s="222"/>
-      <c r="G38" s="222"/>
-      <c r="H38" s="222"/>
-      <c r="I38" s="222"/>
-      <c r="J38" s="222"/>
-      <c r="K38" s="222"/>
-      <c r="L38" s="222"/>
-      <c r="M38" s="222"/>
-      <c r="N38" s="222"/>
-      <c r="O38" s="222"/>
+      <c r="C38" s="225"/>
+      <c r="D38" s="225"/>
+      <c r="E38" s="225"/>
+      <c r="F38" s="225"/>
+      <c r="G38" s="225"/>
+      <c r="H38" s="225"/>
+      <c r="I38" s="225"/>
+      <c r="J38" s="225"/>
+      <c r="K38" s="225"/>
+      <c r="L38" s="225"/>
+      <c r="M38" s="225"/>
+      <c r="N38" s="225"/>
+      <c r="O38" s="225"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4467,13 +4486,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="237" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="236"/>
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="239"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="158"/>
@@ -4528,16 +4547,16 @@
       <c r="E6" s="150"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="237" t="s">
+      <c r="A7" s="240" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="238"/>
-      <c r="C7" s="238"/>
-      <c r="D7" s="238"/>
-      <c r="E7" s="238"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238"/>
-      <c r="H7" s="239"/>
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="241"/>
+      <c r="E7" s="241"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="242"/>
       <c r="L7" s="117" t="s">
         <v>72</v>
       </c>
@@ -5121,13 +5140,13 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B28" s="240" t="s">
+      <c r="B28" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="241"/>
-      <c r="D28" s="241"/>
-      <c r="E28" s="241"/>
-      <c r="F28" s="242"/>
+      <c r="C28" s="244"/>
+      <c r="D28" s="244"/>
+      <c r="E28" s="244"/>
+      <c r="F28" s="245"/>
       <c r="J28" s="117">
         <v>176</v>
       </c>
